--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1181,6 +1181,636 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Paid (30d)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Turbo 10 GB</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Price (R$)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Paid (30d)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Turbo 10 GB</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Paid (30d)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Price (R$)</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Paid (30d)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>TIM Pré XIP Plus</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Paid (30d)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Claro Prezão</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Price (R$)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Paid (30d)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Claro Prezão</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Controle</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle 21 GB</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Controle</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Price (R$)</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>43.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Controle</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Controle</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Claro Controle</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Price (R$)</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>59.9</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós — Entry</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Price (R$)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Price (R$)</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>159.99</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>119.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Claro Pós 70 GB</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Price (R$)</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>119.9</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Claro Pós 70 GB</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1811,6 +1811,384 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Paid (30d)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Claro Prezão</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Controle</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Controle 21 GB</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Controle</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Controle</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Claro Controle</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Vivo Pós — Entry</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Price (R$)</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Price (R$)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>159.99</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>119.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Claro Pós 70 GB</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Price (R$)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>119.9</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Claro Pós 70 GB</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Base Plan GB</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -7,7 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Histórico de Mudanças" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes Log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pré-Pago" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controle" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pós-Pago" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +38,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -87,6 +96,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,6 +466,219 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Hora (BRT)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Segmento</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Plano</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Campo Alterado</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Anterior</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Novo Valor</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Controle</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>TIM Controle</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Preço</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>R$ 49,99</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>— → R$ 49,99</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Preço</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>R$ 159,99</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>R$ 119,99</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>R$ 159,99 → R$ 119,99</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Post-Paid</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>TIM Black A</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>GB Base</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>15 GB</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>70 GB</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15 GB → 70 GB</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2192,4 +2417,454 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Preço (R$)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>GB Base</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bônus</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status Coleta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>+1 GB</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ Verificar manualmente</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>+4 GB</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ Verificar manualmente</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>30,00</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>+10 GB</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ Verificar manualmente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Preço (R$)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>GB Base</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bônus</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status Coleta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>59,00</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>+3 GB / +5 GB</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ Verificar manualmente</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>49,99</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>+10 GB / +6 GB</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>✅ Atualizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>59,90</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>+10 GB</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ Verificar manualmente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Preço (R$)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>GB Base</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bônus</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status Coleta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>140,00</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>+3 GB / +76 GB</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ Verificar manualmente</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>119,99</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>+10 GB / +5 GB</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>✅ Atualizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>119,90</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>+25 GB / +20 GB</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ Verificar manualmente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>